--- a/data-raw/usgs/usgs_um.xlsx
+++ b/data-raw/usgs/usgs_um.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rsericerca-my.sharepoint.com/personal/mela_rse-web_it/Documents/R/miei_pacchetti/clccr/data-raw/usgs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9657111D-FA1E-4C3B-B372-4BF236F36EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{9657111D-FA1E-4C3B-B372-4BF236F36EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28383BBA-38EE-4E6E-B9CD-7F180C188974}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4BA977D8-4E6B-457A-A7D9-6949D1A98AF5}"/>
+    <workbookView xWindow="4260" yWindow="2952" windowWidth="23040" windowHeight="12120" xr2:uid="{4BA977D8-4E6B-457A-A7D9-6949D1A98AF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -500,7 +500,7 @@
   <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
